--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004ppsv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4E61BE-5842-4D59-9DE9-133BBE013E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD2CD49-31A7-42F0-AF01-D3ED0D2BB5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{79564DF6-F3EE-4187-9B62-2720CBE5D5A5}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="297">
   <si>
     <t>cancelado</t>
   </si>
@@ -789,12 +789,6 @@
     <t>1,555.88</t>
   </si>
   <si>
-    <t>592,550.00</t>
-  </si>
-  <si>
-    <t>EM NEGOCIAÇÃO</t>
-  </si>
-  <si>
     <t>ECO FLUID</t>
   </si>
   <si>
@@ -910,6 +904,42 @@
   </si>
   <si>
     <t>EDWARDS VACUO LTDA.</t>
+  </si>
+  <si>
+    <t>630,000.00</t>
+  </si>
+  <si>
+    <t>Travas de Aço Capacitores</t>
+  </si>
+  <si>
+    <t>Acendedor de maçartico e vaselina</t>
+  </si>
+  <si>
+    <t>Trava balancin CA131255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adequação NR12, MQ. De Placa </t>
+  </si>
+  <si>
+    <t>Maquina de Solda Boxer</t>
+  </si>
+  <si>
+    <t>OCTANS SISTEMAS DE AUTOMACAO LTDA.</t>
+  </si>
+  <si>
+    <t>17,175.24</t>
+  </si>
+  <si>
+    <t>26,316.00</t>
+  </si>
+  <si>
+    <t>300.00</t>
+  </si>
+  <si>
+    <t>2,366.00</t>
+  </si>
+  <si>
+    <t>44,925.00</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1066,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1126,11 +1156,110 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="68">
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEBF3FB"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEBF3FB"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEBF3FB"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEBF3FB"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEFFBF1"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -1142,6 +1271,21 @@
           </stop>
           <stop position="1">
             <color theme="0" tint="-5.0965910824915313E-2"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFFEBEB"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1178,6 +1322,36 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0" tint="-5.0965910824915313E-2"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0" tint="-5.0965910824915313E-2"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="9" tint="-0.499984740745262"/>
       </font>
       <fill>
@@ -1187,6 +1361,18 @@
           </stop>
           <stop position="1">
             <color rgb="FFEFFBF1"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFAECF9"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1279,31 +1465,13 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <gradientFill degree="90">
           <stop position="0">
             <color theme="0"/>
           </stop>
           <stop position="1">
-            <color theme="0" tint="-5.0965910824915313E-2"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEFFBF1"/>
+            <color rgb="FFFAECF9"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1324,33 +1492,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFFAECF9"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0" tint="-5.0965910824915313E-2"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color theme="9" tint="-0.499984740745262"/>
       </font>
@@ -1361,33 +1502,6 @@
           </stop>
           <stop position="1">
             <color rgb="FFEFFBF1"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFFFEBEB"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFFAECF9"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1552,6 +1666,51 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFFEBEB"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEFFBF1"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0" tint="-5.0965910824915313E-2"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <gradientFill degree="90">
           <stop position="0">
@@ -1559,6 +1718,51 @@
           </stop>
           <stop position="1">
             <color rgb="FFFAECF9"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEFFBF1"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFFEBEB"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0" tint="-5.0965910824915313E-2"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1625,21 +1829,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFFFEBEB"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -1655,36 +1844,6 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0" tint="-5.0965910824915313E-2"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEFFBF1"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFC00000"/>
       </font>
       <fill>
@@ -1694,51 +1853,6 @@
           </stop>
           <stop position="1">
             <color rgb="FFFFEBEB"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFFFEBEB"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0" tint="-5.0965910824915313E-2"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEFFBF1"/>
           </stop>
         </gradientFill>
       </fill>
@@ -2301,7 +2415,7 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="1" xr9:uid="{FACBFEB2-497A-44CE-885B-1C3836281EDD}">
-      <tableStyleElement type="wholeTable" dxfId="63"/>
+      <tableStyleElement type="wholeTable" dxfId="67"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -7889,32 +8003,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3428ACC8-59A0-43BD-B35D-AF1470BC13C7}" name="Table1" displayName="Table1" ref="A3:M215" totalsRowShown="0" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60">
-  <autoFilter ref="A3:M215" xr:uid="{3428ACC8-59A0-43BD-B35D-AF1470BC13C7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3428ACC8-59A0-43BD-B35D-AF1470BC13C7}" name="Table1" displayName="Table1" ref="A3:M220" totalsRowShown="0" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64">
+  <autoFilter ref="A3:M220" xr:uid="{3428ACC8-59A0-43BD-B35D-AF1470BC13C7}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{BFD5F472-5BB9-40A1-837D-937617438698}" name="Coluna1" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{10F97ABA-649B-4DB5-93A2-73ABBD534859}" name="SOLICITANTE" dataDxfId="58"/>
-    <tableColumn id="12" xr3:uid="{E0E6DF59-9ED2-4C03-B3E6-E8F8C50C4F9D}" name="MODELO" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{5B6F2C6D-B029-4DC2-BD69-A2D5EEBC176D}" name="DESCRIÇÃO" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{A9AA1BF2-EC32-428F-9D4E-7E1CF1FAC7E3}" name="APROVADOR" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{C35FE125-EA24-4AEC-8EE3-41DF793BD8B5}" name="REQUISIÇÃO" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{A5634662-D9E4-4EB9-9ABC-2002ADF14C1E}" name="PEDIDO" dataDxfId="53"/>
-    <tableColumn id="16" xr3:uid="{8211FE9B-3B19-439A-8873-F8C93AC1B4A5}" name="VIM" dataDxfId="52">
+    <tableColumn id="1" xr3:uid="{BFD5F472-5BB9-40A1-837D-937617438698}" name="Coluna1" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{10F97ABA-649B-4DB5-93A2-73ABBD534859}" name="SOLICITANTE" dataDxfId="62"/>
+    <tableColumn id="12" xr3:uid="{E0E6DF59-9ED2-4C03-B3E6-E8F8C50C4F9D}" name="MODELO" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{5B6F2C6D-B029-4DC2-BD69-A2D5EEBC176D}" name="DESCRIÇÃO" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{A9AA1BF2-EC32-428F-9D4E-7E1CF1FAC7E3}" name="APROVADOR" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{C35FE125-EA24-4AEC-8EE3-41DF793BD8B5}" name="REQUISIÇÃO" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{A5634662-D9E4-4EB9-9ABC-2002ADF14C1E}" name="PEDIDO" dataDxfId="57"/>
+    <tableColumn id="16" xr3:uid="{8211FE9B-3B19-439A-8873-F8C93AC1B4A5}" name="VIM" dataDxfId="56">
       <calculatedColumnFormula>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{CB7AE16A-1F61-49F1-BA58-F1C315F391B1}" name="STATUS VIM" dataDxfId="51">
+    <tableColumn id="11" xr3:uid="{CB7AE16A-1F61-49F1-BA58-F1C315F391B1}" name="STATUS VIM" dataDxfId="55">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{70041315-C1E0-4309-8689-2E472489F917}" name="NOTA FISCAL" dataDxfId="50">
+    <tableColumn id="9" xr3:uid="{70041315-C1E0-4309-8689-2E472489F917}" name="NOTA FISCAL" dataDxfId="54">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{C7F9CD0C-F583-4773-9B4B-A43FF813818A}" name="FORNECEDOR" dataDxfId="49">
+    <tableColumn id="7" xr3:uid="{C7F9CD0C-F583-4773-9B4B-A43FF813818A}" name="FORNECEDOR" dataDxfId="53">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!G:G,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B6E5C0E6-2C94-4C09-A090-F0DFB48BA858}" name="DESPESA" dataDxfId="48">
+    <tableColumn id="10" xr3:uid="{B6E5C0E6-2C94-4C09-A090-F0DFB48BA858}" name="DESPESA" dataDxfId="52">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!R:R,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1812DB43-C6D7-4D59-B7F6-73F28ADCBD1D}" name="STATUS" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{1812DB43-C6D7-4D59-B7F6-73F28ADCBD1D}" name="STATUS" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8237,7 +8351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{545EBCB4-4A1F-4CB5-AEB5-88763E37F25E}">
-  <dimension ref="A1:M215"/>
+  <dimension ref="A1:M220"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" style="28" customWidth="1"/>
@@ -8336,7 +8450,7 @@
         <v>8</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>9</v>
@@ -12500,7 +12614,7 @@
         <v>237</v>
       </c>
       <c r="L94" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="M94" s="14" t="s">
         <v>236</v>
@@ -12719,7 +12833,7 @@
         <v>237</v>
       </c>
       <c r="L99" s="15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M99" s="14" t="s">
         <v>236</v>
@@ -14515,7 +14629,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="15" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L140" s="15" t="s">
         <v>240</v>
@@ -14737,10 +14851,10 @@
         <v>0</v>
       </c>
       <c r="K145" s="15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L145" s="15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M145" s="14" t="s">
         <v>236</v>
@@ -14775,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="K146" s="15" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L146" s="15">
         <v>200</v>
@@ -15387,15 +15501,15 @@
       <c r="G160" s="14"/>
       <c r="H160" s="15"/>
       <c r="I160" s="16"/>
-      <c r="J160" s="15">
-        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
-        <v>0</v>
+      <c r="J160" s="15" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
+        <v/>
       </c>
       <c r="K160" s="15" t="s">
         <v>233</v>
       </c>
       <c r="L160" s="15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M160" s="14" t="s">
         <v>236</v>
@@ -15920,15 +16034,15 @@
       </c>
       <c r="H172" s="15"/>
       <c r="I172" s="16"/>
-      <c r="J172" s="15">
-        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
-        <v>0</v>
+      <c r="J172" s="15" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
+        <v/>
       </c>
       <c r="K172" s="15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L172" s="15" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M172" s="14" t="s">
         <v>236</v>
@@ -16015,10 +16129,10 @@
         <v/>
       </c>
       <c r="K174" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L174" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M174" s="14" t="s">
         <v>236</v>
@@ -16049,7 +16163,7 @@
         <v>2990028</v>
       </c>
       <c r="I175" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J175" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -16100,10 +16214,10 @@
         <v/>
       </c>
       <c r="K176" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L176" s="15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="M176" s="14" t="s">
         <v>236</v>
@@ -16446,7 +16560,7 @@
         <v>2993569</v>
       </c>
       <c r="I184" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J184" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -16666,7 +16780,7 @@
         <v>2992797</v>
       </c>
       <c r="I189" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J189" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -16713,10 +16827,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L190" s="15" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M190" s="14" t="s">
         <v>12</v>
@@ -16841,10 +16955,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L193" s="15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M193" s="14" t="s">
         <v>12</v>
@@ -17011,10 +17125,10 @@
         <v>0</v>
       </c>
       <c r="K197" s="15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L197" s="15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M197" s="14" t="s">
         <v>236</v>
@@ -17047,7 +17161,7 @@
         <v>2994677</v>
       </c>
       <c r="I198" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J198" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -17089,10 +17203,10 @@
       <c r="I199" s="16"/>
       <c r="J199" s="15"/>
       <c r="K199" s="15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L199" s="15" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M199" s="14" t="s">
         <v>236</v>
@@ -17124,10 +17238,10 @@
       <c r="I200" s="16"/>
       <c r="J200" s="15"/>
       <c r="K200" s="15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L200" s="15" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M200" s="14" t="s">
         <v>236</v>
@@ -17159,7 +17273,7 @@
       <c r="I201" s="16"/>
       <c r="J201" s="15"/>
       <c r="K201" s="15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L201" s="29">
         <v>1990</v>
@@ -17195,7 +17309,7 @@
         <v>2997755</v>
       </c>
       <c r="I202" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J202" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -17239,10 +17353,10 @@
       <c r="I203" s="16"/>
       <c r="J203" s="15"/>
       <c r="K203" s="15" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L203" s="15" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="M203" s="14" t="s">
         <v>236</v>
@@ -17274,10 +17388,10 @@
       <c r="I204" s="16"/>
       <c r="J204" s="15"/>
       <c r="K204" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L204" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M204" s="14" t="s">
         <v>236</v>
@@ -17309,10 +17423,10 @@
       <c r="I205" s="16"/>
       <c r="J205" s="15"/>
       <c r="K205" s="15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L205" s="15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M205" s="14" t="s">
         <v>236</v>
@@ -17347,7 +17461,7 @@
         <v>244</v>
       </c>
       <c r="L206" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M206" s="14" t="s">
         <v>236</v>
@@ -17379,10 +17493,10 @@
       <c r="I207" s="16"/>
       <c r="J207" s="15"/>
       <c r="K207" s="15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L207" s="15" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M207" s="14" t="s">
         <v>236</v>
@@ -17414,7 +17528,7 @@
       <c r="I208" s="16"/>
       <c r="J208" s="15"/>
       <c r="K208" s="15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L208" s="29">
         <v>1622.82</v>
@@ -17447,10 +17561,10 @@
       <c r="I209" s="16"/>
       <c r="J209" s="15"/>
       <c r="K209" s="15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L209" s="15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M209" s="14" t="s">
         <v>236</v>
@@ -17482,10 +17596,10 @@
       <c r="I210" s="16"/>
       <c r="J210" s="15"/>
       <c r="K210" s="15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L210" s="15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="M210" s="14" t="s">
         <v>236</v>
@@ -17515,13 +17629,13 @@
       <c r="I211" s="16"/>
       <c r="J211" s="15"/>
       <c r="K211" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L211" s="15" t="s">
-        <v>246</v>
+        <v>285</v>
       </c>
       <c r="M211" s="14" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.3">
@@ -17537,7 +17651,9 @@
       <c r="D212" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="E212" s="20"/>
+      <c r="E212" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="F212" s="19">
         <v>1078966324</v>
       </c>
@@ -17605,16 +17721,20 @@
       <c r="D214" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="E214" s="20"/>
+      <c r="E214" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="F214" s="19">
         <v>1078978713</v>
       </c>
-      <c r="G214" s="14"/>
+      <c r="G214" s="14">
+        <v>4501747547</v>
+      </c>
       <c r="H214" s="15"/>
       <c r="I214" s="16"/>
       <c r="J214" s="15"/>
       <c r="K214" s="15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L214" s="15" t="s">
         <v>242</v>
@@ -17636,11 +17756,15 @@
       <c r="D215" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E215" s="20"/>
+      <c r="E215" s="20" t="s">
+        <v>109</v>
+      </c>
       <c r="F215" s="19">
         <v>1078985294</v>
       </c>
-      <c r="G215" s="14"/>
+      <c r="G215" s="14">
+        <v>4501745495</v>
+      </c>
       <c r="H215" s="15"/>
       <c r="I215" s="16"/>
       <c r="J215" s="15"/>
@@ -17654,193 +17778,415 @@
         <v>236</v>
       </c>
     </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A216" s="38">
+        <v>46174</v>
+      </c>
+      <c r="B216" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="C216" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D216" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="E216" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="F216" s="42">
+        <v>1079039866</v>
+      </c>
+      <c r="G216" s="34">
+        <v>4501746806</v>
+      </c>
+      <c r="H216" s="35" t="str">
+        <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I216" s="36" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
+        <v/>
+      </c>
+      <c r="J216" s="37" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
+        <v/>
+      </c>
+      <c r="K216" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="L216" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="M216" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A217" s="31">
+        <v>46174</v>
+      </c>
+      <c r="B217" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C217" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D217" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="E217" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F217" s="19">
+        <v>1079039867</v>
+      </c>
+      <c r="G217" s="34"/>
+      <c r="H217" s="35" t="str">
+        <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I217" s="36" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
+        <v/>
+      </c>
+      <c r="J217" s="37" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
+        <v/>
+      </c>
+      <c r="K217" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="L217" s="35" t="s">
+        <v>295</v>
+      </c>
+      <c r="M217" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A218" s="31">
+        <v>46175</v>
+      </c>
+      <c r="B218" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C218" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D218" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="E218" s="33"/>
+      <c r="F218" s="19">
+        <v>1079040130</v>
+      </c>
+      <c r="G218" s="34"/>
+      <c r="H218" s="35" t="str">
+        <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I218" s="36" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
+        <v/>
+      </c>
+      <c r="J218" s="37" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
+        <v/>
+      </c>
+      <c r="K218" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="L218" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="M218" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A219" s="31">
+        <v>46182</v>
+      </c>
+      <c r="B219" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C219" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D219" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="E219" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="F219" s="19">
+        <v>1079140236</v>
+      </c>
+      <c r="G219" s="34"/>
+      <c r="H219" s="35" t="str">
+        <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I219" s="36" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
+        <v/>
+      </c>
+      <c r="J219" s="37" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
+        <v/>
+      </c>
+      <c r="K219" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="L219" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="M219" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A220" s="38">
+        <v>46182</v>
+      </c>
+      <c r="B220" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="C220" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D220" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="E220" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="F220" s="19">
+        <v>1079174969</v>
+      </c>
+      <c r="G220" s="14">
+        <v>4501749108</v>
+      </c>
+      <c r="H220" s="35" t="str">
+        <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I220" s="36" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
+        <v/>
+      </c>
+      <c r="J220" s="37" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
+        <v/>
+      </c>
+      <c r="K220" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="L220" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="M220" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A4:F215">
-    <cfRule type="expression" dxfId="46" priority="51">
+  <conditionalFormatting sqref="A4:F216 A217:E220">
+    <cfRule type="expression" dxfId="50" priority="53">
       <formula>$F4&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A206:F206">
-    <cfRule type="expression" dxfId="45" priority="53">
+    <cfRule type="expression" dxfId="49" priority="55">
       <formula>#REF!&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A207:F207">
-    <cfRule type="expression" dxfId="44" priority="52">
+    <cfRule type="expression" dxfId="48" priority="54">
       <formula>$G206&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:G205 E206:E211 A208:D208 F208:G208 G206">
-    <cfRule type="expression" dxfId="43" priority="50">
+    <cfRule type="expression" dxfId="47" priority="52">
       <formula>$G4&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A203:K204 A205:J205 H206:J206 F206:F207 A206:D208 E206:E211 H207:K207 F208:K208 A4:L202">
-    <cfRule type="expression" dxfId="42" priority="49">
+  <conditionalFormatting sqref="A4:L202 A203:K204 A205:J205 H206:J206 F206:F207 A206:D208 E206:E211 H207:K207 F208:K208">
+    <cfRule type="expression" dxfId="46" priority="51">
       <formula>$K4&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A189:L189">
-    <cfRule type="expression" dxfId="41" priority="68">
-      <formula>#REF!="finalizado"</formula>
+    <cfRule type="expression" dxfId="45" priority="71">
+      <formula>#REF!="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="67">
+    <cfRule type="expression" dxfId="44" priority="69">
       <formula>#REF!="quadro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="69">
-      <formula>#REF!="cancelado"</formula>
+    <cfRule type="expression" dxfId="43" priority="70">
+      <formula>#REF!="finalizado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A190:L190">
-    <cfRule type="expression" dxfId="38" priority="66">
+    <cfRule type="expression" dxfId="42" priority="67">
+      <formula>$M189="finalizado"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="68">
       <formula>$M189="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="65">
-      <formula>$M189="finalizado"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="64">
+    <cfRule type="expression" dxfId="40" priority="66">
       <formula>$M189="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M189:M194 A191:M201 A202:L202 A203:K204 A205:J205 H206:J206 F206:F207 A206:D208 E206:E211 H207:K207 F208:K208 A4:M188">
-    <cfRule type="expression" dxfId="35" priority="46">
+  <conditionalFormatting sqref="A4:M188 M189:M194 A191:M201 A202:L202 A203:K204 A205:J205 H206:J206 F206:F207 A206:D208 E206:E211 H207:K207 F208:K208">
+    <cfRule type="expression" dxfId="39" priority="48">
       <formula>$M4="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M189:M194 A191:M201 M201:M209 A202:L202 A203:K204 A205:J205 H206:J206 F206:F207 A206:D208 E206:E211 H207:K207 F208:K208 A4:M188">
-    <cfRule type="expression" dxfId="34" priority="48">
+  <conditionalFormatting sqref="A4:M188 M189:M194 A191:M201 M201:M209 A202:L202 A203:K204 A205:J205 H206:J206 F206:F207 A206:D208 E206:E211 H207:K207 F208:K208">
+    <cfRule type="expression" dxfId="38" priority="50">
       <formula>$M4="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="47">
+    <cfRule type="expression" dxfId="37" priority="49">
       <formula>$M4="finalizado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G206">
-    <cfRule type="expression" dxfId="32" priority="56">
+    <cfRule type="expression" dxfId="36" priority="56">
+      <formula>$K207&lt;&gt;""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="57">
+      <formula>$M207="quadro"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="58">
       <formula>$M207="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="57">
+    <cfRule type="expression" dxfId="33" priority="59">
       <formula>$M207="cancelado"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="55">
-      <formula>$M207="quadro"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="54">
-      <formula>$K207&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L2">
-    <cfRule type="expression" dxfId="28" priority="45">
+    <cfRule type="expression" dxfId="32" priority="47">
       <formula>$K2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:M2">
-    <cfRule type="expression" dxfId="27" priority="44">
+    <cfRule type="expression" dxfId="31" priority="46">
       <formula>$M2="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="43">
+    <cfRule type="expression" dxfId="30" priority="45">
       <formula>$M2="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="42">
+    <cfRule type="expression" dxfId="29" priority="44">
       <formula>$M2="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I189:I190">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="28" priority="3">
       <formula>$M189="quadro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="2">
+    <cfRule type="expression" dxfId="27" priority="4">
       <formula>$M189="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="3">
+    <cfRule type="expression" dxfId="26" priority="5">
       <formula>$M189="cancelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I209">
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="25" priority="21">
       <formula>$M209="quadro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="24" priority="22">
       <formula>$M209="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="23" priority="23">
       <formula>$M209="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="22">
+    <cfRule type="expression" dxfId="22" priority="24">
       <formula>$K209&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I211">
-    <cfRule type="expression" dxfId="17" priority="14">
+    <cfRule type="expression" dxfId="21" priority="14">
+      <formula>$M211="finalizado"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="15">
+      <formula>$M211="cancelado"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="16">
       <formula>$K211&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="13">
-      <formula>$M211="cancelado"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="12">
-      <formula>$M211="finalizado"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="11">
+    <cfRule type="expression" dxfId="18" priority="13">
       <formula>$M211="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I213">
-    <cfRule type="expression" dxfId="13" priority="26">
+    <cfRule type="expression" dxfId="17" priority="28">
       <formula>$K213&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="25">
+    <cfRule type="expression" dxfId="16" priority="27">
       <formula>$M213="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="24">
+    <cfRule type="expression" dxfId="15" priority="26">
       <formula>$M213="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="23">
+    <cfRule type="expression" dxfId="14" priority="25">
       <formula>$M213="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I215">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="13" priority="8">
+      <formula>$M215="cancelado"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="9">
+      <formula>$K215&lt;&gt;""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="7">
+      <formula>$M215="finalizado"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>$M215="quadro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="7">
-      <formula>$K215&lt;&gt;""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="6">
-      <formula>$M215="cancelado"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="5">
-      <formula>$M215="finalizado"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M201:M210">
-    <cfRule type="expression" dxfId="5" priority="27">
+  <conditionalFormatting sqref="M201:M210 M216">
+    <cfRule type="expression" dxfId="9" priority="29">
       <formula>$M201="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M210">
-    <cfRule type="expression" dxfId="4" priority="29">
+  <conditionalFormatting sqref="M210 M216">
+    <cfRule type="expression" dxfId="8" priority="31">
       <formula>$M210="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="28">
+    <cfRule type="expression" dxfId="7" priority="30">
       <formula>$M210="finalizado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M212:M215">
-    <cfRule type="expression" dxfId="2" priority="32">
+  <conditionalFormatting sqref="M212:M215 M218:M220">
+    <cfRule type="expression" dxfId="6" priority="34">
       <formula>$M212="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="31">
+    <cfRule type="expression" dxfId="5" priority="32">
+      <formula>$M212="quadro"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="33">
       <formula>$M212="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="30">
-      <formula>$M212="quadro"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A217:D220">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$F217&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F217:F220">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$F217&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E215" xr:uid="{662CF013-9546-42FB-8294-F5B66BB746FC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E220" xr:uid="{662CF013-9546-42FB-8294-F5B66BB746FC}">
       <formula1>"Marco Stella, Rodrigo Zerneri, Adriana Silva"</formula1>
     </dataValidation>
   </dataValidations>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004ppsv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD2CD49-31A7-42F0-AF01-D3ED0D2BB5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB7B175-C47C-47D5-8F2F-7DFE2B3ADC76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{79564DF6-F3EE-4187-9B62-2720CBE5D5A5}"/>
   </bookViews>
@@ -885,9 +885,6 @@
     <t>TEC JATO</t>
   </si>
   <si>
-    <t>1.250,000.00</t>
-  </si>
-  <si>
     <t>DESPESA</t>
   </si>
   <si>
@@ -940,6 +937,9 @@
   </si>
   <si>
     <t>44,925.00</t>
+  </si>
+  <si>
+    <t>1,250,000.00</t>
   </si>
 </sst>
 </file>
@@ -8450,7 +8450,7 @@
         <v>8</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>9</v>
@@ -14629,7 +14629,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L140" s="15" t="s">
         <v>240</v>
@@ -16217,7 +16217,7 @@
         <v>277</v>
       </c>
       <c r="L176" s="15" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="M176" s="14" t="s">
         <v>236</v>
@@ -16830,7 +16830,7 @@
         <v>271</v>
       </c>
       <c r="L190" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M190" s="14" t="s">
         <v>12</v>
@@ -17203,7 +17203,7 @@
       <c r="I199" s="16"/>
       <c r="J199" s="15"/>
       <c r="K199" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L199" s="15" t="s">
         <v>260</v>
@@ -17599,7 +17599,7 @@
         <v>247</v>
       </c>
       <c r="L210" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M210" s="14" t="s">
         <v>236</v>
@@ -17632,7 +17632,7 @@
         <v>246</v>
       </c>
       <c r="L211" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M211" s="14" t="s">
         <v>236</v>
@@ -17734,7 +17734,7 @@
       <c r="I214" s="16"/>
       <c r="J214" s="15"/>
       <c r="K214" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L214" s="15" t="s">
         <v>242</v>
@@ -17789,7 +17789,7 @@
         <v>10</v>
       </c>
       <c r="D216" s="40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E216" s="41" t="s">
         <v>109</v>
@@ -17816,7 +17816,7 @@
         <v>255</v>
       </c>
       <c r="L216" s="35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M216" s="14" t="s">
         <v>236</v>
@@ -17833,7 +17833,7 @@
         <v>10</v>
       </c>
       <c r="D217" s="40" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E217" s="33" t="s">
         <v>11</v>
@@ -17858,7 +17858,7 @@
         <v>244</v>
       </c>
       <c r="L217" s="35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M217" s="14" t="s">
         <v>236</v>
@@ -17875,7 +17875,7 @@
         <v>10</v>
       </c>
       <c r="D218" s="40" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E218" s="33"/>
       <c r="F218" s="19">
@@ -17898,7 +17898,7 @@
         <v>259</v>
       </c>
       <c r="L218" s="35" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M218" s="14" t="s">
         <v>236</v>
@@ -17915,7 +17915,7 @@
         <v>25</v>
       </c>
       <c r="D219" s="40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E219" s="33" t="s">
         <v>109</v>
@@ -17937,10 +17937,10 @@
         <v/>
       </c>
       <c r="K219" s="35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L219" s="35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M219" s="14" t="s">
         <v>236</v>
@@ -17957,7 +17957,7 @@
         <v>25</v>
       </c>
       <c r="D220" s="40" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E220" s="41" t="s">
         <v>109</v>
@@ -17984,7 +17984,7 @@
         <v>233</v>
       </c>
       <c r="L220" s="35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M220" s="14" t="s">
         <v>236</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004ppsv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB7B175-C47C-47D5-8F2F-7DFE2B3ADC76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A42E253-F60F-45E8-BD90-6BE5949E9657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{79564DF6-F3EE-4187-9B62-2720CBE5D5A5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79564DF6-F3EE-4187-9B62-2720CBE5D5A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Requisições FY26" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="296">
   <si>
     <t>cancelado</t>
   </si>
@@ -471,9 +471,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jogos de macho </t>
-  </si>
-  <si>
-    <t>OI 2352918</t>
   </si>
   <si>
     <t xml:space="preserve"> OI - Contador de Partículas</t>
@@ -1066,7 +1063,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1156,110 +1153,11 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEBF3FB"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEBF3FB"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEBF3FB"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEBF3FB"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEFFBF1"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
+  <dxfs count="66">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1286,6 +1184,21 @@
           </stop>
           <stop position="1">
             <color rgb="FFFFEBEB"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEFFBF1"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1337,21 +1250,6 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0" tint="-5.0965910824915313E-2"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="9" tint="-0.499984740745262"/>
       </font>
       <fill>
@@ -1361,33 +1259,6 @@
           </stop>
           <stop position="1">
             <color rgb="FFEFFBF1"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFFAECF9"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFFFEBEB"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1403,21 +1274,6 @@
           </stop>
           <stop position="1">
             <color theme="0" tint="-5.0965910824915313E-2"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEFFBF1"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1465,6 +1321,78 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFFEBEB"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFAECF9"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEFFBF1"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEFFBF1"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0" tint="-5.0965910824915313E-2"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <gradientFill degree="90">
           <stop position="0">
@@ -1487,21 +1415,6 @@
           </stop>
           <stop position="1">
             <color rgb="FFFFEBEB"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFEFFBF1"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1723,6 +1636,18 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEBF3FB"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="9" tint="-0.499984740745262"/>
       </font>
@@ -1769,21 +1694,6 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0" tint="-5.0965910824915313E-2"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFC00000"/>
       </font>
       <fill>
@@ -1808,6 +1718,21 @@
           </stop>
           <stop position="1">
             <color rgb="FFEFFBF1"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0" tint="-5.0965910824915313E-2"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1901,6 +1826,18 @@
           </stop>
           <stop position="1">
             <color rgb="FFFEF5DA"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFEBF3FB"/>
           </stop>
         </gradientFill>
       </fill>
@@ -2415,7 +2352,7 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="1" xr9:uid="{FACBFEB2-497A-44CE-885B-1C3836281EDD}">
-      <tableStyleElement type="wholeTable" dxfId="67"/>
+      <tableStyleElement type="wholeTable" dxfId="65"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -8003,32 +7940,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3428ACC8-59A0-43BD-B35D-AF1470BC13C7}" name="Table1" displayName="Table1" ref="A3:M220" totalsRowShown="0" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3428ACC8-59A0-43BD-B35D-AF1470BC13C7}" name="Table1" displayName="Table1" ref="A3:M220" totalsRowShown="0" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62">
   <autoFilter ref="A3:M220" xr:uid="{3428ACC8-59A0-43BD-B35D-AF1470BC13C7}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{BFD5F472-5BB9-40A1-837D-937617438698}" name="Coluna1" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{10F97ABA-649B-4DB5-93A2-73ABBD534859}" name="SOLICITANTE" dataDxfId="62"/>
-    <tableColumn id="12" xr3:uid="{E0E6DF59-9ED2-4C03-B3E6-E8F8C50C4F9D}" name="MODELO" dataDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{5B6F2C6D-B029-4DC2-BD69-A2D5EEBC176D}" name="DESCRIÇÃO" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{A9AA1BF2-EC32-428F-9D4E-7E1CF1FAC7E3}" name="APROVADOR" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{C35FE125-EA24-4AEC-8EE3-41DF793BD8B5}" name="REQUISIÇÃO" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{A5634662-D9E4-4EB9-9ABC-2002ADF14C1E}" name="PEDIDO" dataDxfId="57"/>
-    <tableColumn id="16" xr3:uid="{8211FE9B-3B19-439A-8873-F8C93AC1B4A5}" name="VIM" dataDxfId="56">
+    <tableColumn id="1" xr3:uid="{BFD5F472-5BB9-40A1-837D-937617438698}" name="Coluna1" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{10F97ABA-649B-4DB5-93A2-73ABBD534859}" name="SOLICITANTE" dataDxfId="60"/>
+    <tableColumn id="12" xr3:uid="{E0E6DF59-9ED2-4C03-B3E6-E8F8C50C4F9D}" name="MODELO" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{5B6F2C6D-B029-4DC2-BD69-A2D5EEBC176D}" name="DESCRIÇÃO" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{A9AA1BF2-EC32-428F-9D4E-7E1CF1FAC7E3}" name="APROVADOR" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{C35FE125-EA24-4AEC-8EE3-41DF793BD8B5}" name="REQUISIÇÃO" dataDxfId="56"/>
+    <tableColumn id="6" xr3:uid="{A5634662-D9E4-4EB9-9ABC-2002ADF14C1E}" name="PEDIDO" dataDxfId="55"/>
+    <tableColumn id="16" xr3:uid="{8211FE9B-3B19-439A-8873-F8C93AC1B4A5}" name="VIM" dataDxfId="54">
       <calculatedColumnFormula>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{CB7AE16A-1F61-49F1-BA58-F1C315F391B1}" name="STATUS VIM" dataDxfId="55">
+    <tableColumn id="11" xr3:uid="{CB7AE16A-1F61-49F1-BA58-F1C315F391B1}" name="STATUS VIM" dataDxfId="53">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{70041315-C1E0-4309-8689-2E472489F917}" name="NOTA FISCAL" dataDxfId="54">
+    <tableColumn id="9" xr3:uid="{70041315-C1E0-4309-8689-2E472489F917}" name="NOTA FISCAL" dataDxfId="52">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{C7F9CD0C-F583-4773-9B4B-A43FF813818A}" name="FORNECEDOR" dataDxfId="53">
+    <tableColumn id="7" xr3:uid="{C7F9CD0C-F583-4773-9B4B-A43FF813818A}" name="FORNECEDOR" dataDxfId="51">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!G:G,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B6E5C0E6-2C94-4C09-A090-F0DFB48BA858}" name="DESPESA" dataDxfId="52">
+    <tableColumn id="10" xr3:uid="{B6E5C0E6-2C94-4C09-A090-F0DFB48BA858}" name="DESPESA" dataDxfId="50">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!R:R,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1812DB43-C6D7-4D59-B7F6-73F28ADCBD1D}" name="STATUS" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{1812DB43-C6D7-4D59-B7F6-73F28ADCBD1D}" name="STATUS" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8371,7 +8308,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -8417,16 +8354,16 @@
     </row>
     <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
@@ -8450,7 +8387,7 @@
         <v>8</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>9</v>
@@ -8461,7 +8398,7 @@
         <v>45874</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>10</v>
@@ -8507,7 +8444,7 @@
         <v>45874</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>13</v>
@@ -8553,7 +8490,7 @@
         <v>45881</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>10</v>
@@ -8599,7 +8536,7 @@
         <v>45881</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>10</v>
@@ -8645,7 +8582,7 @@
         <v>45881</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>10</v>
@@ -8691,7 +8628,7 @@
         <v>45888</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>10</v>
@@ -8737,7 +8674,7 @@
         <v>45888</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>10</v>
@@ -8783,7 +8720,7 @@
         <v>45888</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>10</v>
@@ -8829,7 +8766,7 @@
         <v>45890</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>10</v>
@@ -8875,7 +8812,7 @@
         <v>45896</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>10</v>
@@ -8921,7 +8858,7 @@
         <v>45896</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>13</v>
@@ -8967,7 +8904,7 @@
         <v>45897</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>25</v>
@@ -9013,7 +8950,7 @@
         <v>45897</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>25</v>
@@ -9059,7 +8996,7 @@
         <v>45897</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>25</v>
@@ -9102,7 +9039,7 @@
         <v>45897</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>25</v>
@@ -9148,7 +9085,7 @@
         <v>45897</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>25</v>
@@ -9194,7 +9131,7 @@
         <v>45897</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>25</v>
@@ -9240,7 +9177,7 @@
         <v>45897</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>25</v>
@@ -9281,7 +9218,7 @@
         <v>45897</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>25</v>
@@ -9327,7 +9264,7 @@
         <v>45897</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>25</v>
@@ -9373,7 +9310,7 @@
         <v>45901</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>10</v>
@@ -9419,7 +9356,7 @@
         <v>45903</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>10</v>
@@ -9465,7 +9402,7 @@
         <v>45903</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>10</v>
@@ -9511,7 +9448,7 @@
         <v>45903</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>10</v>
@@ -9557,7 +9494,7 @@
         <v>45903</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>10</v>
@@ -9603,7 +9540,7 @@
         <v>45912</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>10</v>
@@ -9649,7 +9586,7 @@
         <v>45915</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>10</v>
@@ -9695,7 +9632,7 @@
         <v>45916</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>10</v>
@@ -9741,7 +9678,7 @@
         <v>45916</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>10</v>
@@ -9787,7 +9724,7 @@
         <v>45917</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>10</v>
@@ -9833,7 +9770,7 @@
         <v>45918</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>10</v>
@@ -9879,7 +9816,7 @@
         <v>45922</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>10</v>
@@ -9925,7 +9862,7 @@
         <v>45924</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>10</v>
@@ -9971,7 +9908,7 @@
         <v>45925</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>10</v>
@@ -10017,7 +9954,7 @@
         <v>45926</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>10</v>
@@ -10063,7 +10000,7 @@
         <v>45926</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>10</v>
@@ -10109,7 +10046,7 @@
         <v>45930</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>10</v>
@@ -10155,7 +10092,7 @@
         <v>45930</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>10</v>
@@ -10201,7 +10138,7 @@
         <v>45930</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>10</v>
@@ -10247,7 +10184,7 @@
         <v>45931</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>10</v>
@@ -10293,7 +10230,7 @@
         <v>45931</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>10</v>
@@ -10339,7 +10276,7 @@
         <v>45931</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>10</v>
@@ -10385,7 +10322,7 @@
         <v>45936</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>10</v>
@@ -10431,7 +10368,7 @@
         <v>45937</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>10</v>
@@ -10477,7 +10414,7 @@
         <v>45938</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>10</v>
@@ -10523,7 +10460,7 @@
         <v>45939</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>10</v>
@@ -10569,7 +10506,7 @@
         <v>45940</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>10</v>
@@ -10615,7 +10552,7 @@
         <v>45941</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>10</v>
@@ -10661,7 +10598,7 @@
         <v>45942</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>10</v>
@@ -10707,7 +10644,7 @@
         <v>45943</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>10</v>
@@ -10753,7 +10690,7 @@
         <v>45944</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>10</v>
@@ -10799,7 +10736,7 @@
         <v>45945</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>10</v>
@@ -10845,7 +10782,7 @@
         <v>45946</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>10</v>
@@ -10891,7 +10828,7 @@
         <v>45952</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>10</v>
@@ -10937,7 +10874,7 @@
         <v>45952</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>10</v>
@@ -10983,7 +10920,7 @@
         <v>45953</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>10</v>
@@ -11029,7 +10966,7 @@
         <v>45957</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>10</v>
@@ -11075,7 +11012,7 @@
         <v>45958</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>13</v>
@@ -11121,7 +11058,7 @@
         <v>45960</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>10</v>
@@ -11167,7 +11104,7 @@
         <v>45961</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>10</v>
@@ -11213,7 +11150,7 @@
         <v>45966</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>10</v>
@@ -11259,7 +11196,7 @@
         <v>45966</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>10</v>
@@ -11305,7 +11242,7 @@
         <v>45966</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>10</v>
@@ -11351,7 +11288,7 @@
         <v>45966</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>10</v>
@@ -11397,7 +11334,7 @@
         <v>45966</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>10</v>
@@ -11443,7 +11380,7 @@
         <v>45971</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>10</v>
@@ -11489,7 +11426,7 @@
         <v>45971</v>
       </c>
       <c r="B70" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>10</v>
@@ -11535,7 +11472,7 @@
         <v>45974</v>
       </c>
       <c r="B71" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>10</v>
@@ -11581,7 +11518,7 @@
         <v>45975</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>10</v>
@@ -11627,7 +11564,7 @@
         <v>45975</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>10</v>
@@ -11673,7 +11610,7 @@
         <v>45978</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>10</v>
@@ -11719,7 +11656,7 @@
         <v>45978</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C75" s="11" t="s">
         <v>10</v>
@@ -11765,7 +11702,7 @@
         <v>45979</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>10</v>
@@ -11811,7 +11748,7 @@
         <v>45993</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C77" s="11" t="s">
         <v>10</v>
@@ -11857,7 +11794,7 @@
         <v>45993</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>10</v>
@@ -11903,7 +11840,7 @@
         <v>45993</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>13</v>
@@ -11946,7 +11883,7 @@
         <v>45993</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>10</v>
@@ -11992,7 +11929,7 @@
         <v>45993</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>10</v>
@@ -12038,7 +11975,7 @@
         <v>45993</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>10</v>
@@ -12084,7 +12021,7 @@
         <v>45993</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C83" s="11" t="s">
         <v>10</v>
@@ -12130,7 +12067,7 @@
         <v>46000</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>10</v>
@@ -12176,7 +12113,7 @@
         <v>46000</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>10</v>
@@ -12222,7 +12159,7 @@
         <v>46002</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>10</v>
@@ -12268,7 +12205,7 @@
         <v>46002</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>10</v>
@@ -12314,7 +12251,7 @@
         <v>46002</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>10</v>
@@ -12360,7 +12297,7 @@
         <v>46028</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>10</v>
@@ -12406,7 +12343,7 @@
         <v>46029</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>10</v>
@@ -12452,7 +12389,7 @@
         <v>46029</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C91" s="11" t="s">
         <v>10</v>
@@ -12498,7 +12435,7 @@
         <v>46029</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>10</v>
@@ -12544,7 +12481,7 @@
         <v>46031</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>13</v>
@@ -12590,7 +12527,7 @@
         <v>46034</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>13</v>
@@ -12611,13 +12548,13 @@
       <c r="I94" s="16"/>
       <c r="J94" s="15"/>
       <c r="K94" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L94" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M94" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
@@ -12625,7 +12562,7 @@
         <v>46034</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>10</v>
@@ -12671,7 +12608,7 @@
         <v>46034</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>10</v>
@@ -12717,7 +12654,7 @@
         <v>46034</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>10</v>
@@ -12763,7 +12700,7 @@
         <v>46036</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>10</v>
@@ -12809,7 +12746,7 @@
         <v>46037</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>25</v>
@@ -12830,13 +12767,13 @@
       <c r="I99" s="16"/>
       <c r="J99" s="15"/>
       <c r="K99" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L99" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M99" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
@@ -12844,7 +12781,7 @@
         <v>46037</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>13</v>
@@ -12890,7 +12827,7 @@
         <v>46037</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>13</v>
@@ -12936,7 +12873,7 @@
         <v>46037</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>25</v>
@@ -12979,7 +12916,7 @@
         <v>46043</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>10</v>
@@ -13025,7 +12962,7 @@
         <v>46043</v>
       </c>
       <c r="B104" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>10</v>
@@ -13071,7 +13008,7 @@
         <v>46043</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>13</v>
@@ -13114,7 +13051,7 @@
         <v>46043</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>10</v>
@@ -13160,7 +13097,7 @@
         <v>46043</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>10</v>
@@ -13206,7 +13143,7 @@
         <v>46043</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>10</v>
@@ -13252,7 +13189,7 @@
         <v>46044</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C109" s="11" t="s">
         <v>10</v>
@@ -13298,7 +13235,7 @@
         <v>46045</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>10</v>
@@ -13344,7 +13281,7 @@
         <v>46045</v>
       </c>
       <c r="B111" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>10</v>
@@ -13556,7 +13493,7 @@
         <v>46051</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C116" s="11" t="s">
         <v>10</v>
@@ -13600,7 +13537,7 @@
         <v>46051</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C117" s="11" t="s">
         <v>10</v>
@@ -13644,7 +13581,7 @@
         <v>46052</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>10</v>
@@ -13688,7 +13625,7 @@
         <v>46055</v>
       </c>
       <c r="B119" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C119" s="11" t="s">
         <v>10</v>
@@ -13724,7 +13661,7 @@
         <v>2,932.98</v>
       </c>
       <c r="M119" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
@@ -13732,7 +13669,7 @@
         <v>46055</v>
       </c>
       <c r="B120" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C120" s="11" t="s">
         <v>10</v>
@@ -13776,7 +13713,7 @@
         <v>46056</v>
       </c>
       <c r="B121" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C121" s="11" t="s">
         <v>10</v>
@@ -13820,7 +13757,7 @@
         <v>46056</v>
       </c>
       <c r="B122" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C122" s="11" t="s">
         <v>10</v>
@@ -13864,7 +13801,7 @@
         <v>46057</v>
       </c>
       <c r="B123" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C123" s="11" t="s">
         <v>10</v>
@@ -13908,7 +13845,7 @@
         <v>46057</v>
       </c>
       <c r="B124" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C124" s="11" t="s">
         <v>10</v>
@@ -13952,7 +13889,7 @@
         <v>46058</v>
       </c>
       <c r="B125" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C125" s="11" t="s">
         <v>10</v>
@@ -14038,7 +13975,7 @@
         <v>45697</v>
       </c>
       <c r="B127" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C127" s="11" t="s">
         <v>10</v>
@@ -14082,7 +14019,7 @@
         <v>45697</v>
       </c>
       <c r="B128" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C128" s="11" t="s">
         <v>10</v>
@@ -14126,7 +14063,7 @@
         <v>45697</v>
       </c>
       <c r="B129" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C129" s="11" t="s">
         <v>10</v>
@@ -14293,7 +14230,7 @@
         <v>46066</v>
       </c>
       <c r="B133" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C133" s="11" t="s">
         <v>10</v>
@@ -14337,13 +14274,13 @@
         <v>46066</v>
       </c>
       <c r="B134" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C134" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D134" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D134" s="17" t="s">
-        <v>144</v>
       </c>
       <c r="E134" s="12" t="s">
         <v>109</v>
@@ -14380,13 +14317,13 @@
         <v>46066</v>
       </c>
       <c r="B135" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C135" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E135" s="12" t="s">
         <v>109</v>
@@ -14426,13 +14363,13 @@
         <v>46066</v>
       </c>
       <c r="B136" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E136" s="12" t="s">
         <v>109</v>
@@ -14472,13 +14409,13 @@
         <v>46066</v>
       </c>
       <c r="B137" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C137" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E137" s="12" t="s">
         <v>109</v>
@@ -14518,13 +14455,13 @@
         <v>46066</v>
       </c>
       <c r="B138" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E138" s="12" t="s">
         <v>109</v>
@@ -14565,7 +14502,7 @@
         <v>25</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E139" s="12" t="s">
         <v>109</v>
@@ -14605,13 +14542,13 @@
         <v>46073</v>
       </c>
       <c r="B140" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E140" s="12" t="s">
         <v>109</v>
@@ -14629,13 +14566,13 @@
         <v>0</v>
       </c>
       <c r="K140" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L140" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M140" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.3">
@@ -14643,13 +14580,13 @@
         <v>46073</v>
       </c>
       <c r="B141" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E141" s="12" t="s">
         <v>109</v>
@@ -14689,13 +14626,13 @@
         <v>46073</v>
       </c>
       <c r="B142" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E142" s="12" t="s">
         <v>109</v>
@@ -14735,13 +14672,13 @@
         <v>46080</v>
       </c>
       <c r="B143" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E143" s="12" t="s">
         <v>109</v>
@@ -14781,13 +14718,13 @@
         <v>46080</v>
       </c>
       <c r="B144" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E144" s="12" t="s">
         <v>109</v>
@@ -14827,13 +14764,13 @@
         <v>46083</v>
       </c>
       <c r="B145" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E145" s="12" t="s">
         <v>109</v>
@@ -14851,13 +14788,13 @@
         <v>0</v>
       </c>
       <c r="K145" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="L145" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="L145" s="15" t="s">
-        <v>269</v>
-      </c>
       <c r="M145" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.3">
@@ -14865,13 +14802,13 @@
         <v>46083</v>
       </c>
       <c r="B146" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E146" s="12" t="s">
         <v>109</v>
@@ -14889,7 +14826,7 @@
         <v>0</v>
       </c>
       <c r="K146" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L146" s="15">
         <v>200</v>
@@ -14903,13 +14840,13 @@
         <v>46085</v>
       </c>
       <c r="B147" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C147" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D147" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E147" s="12" t="s">
         <v>109</v>
@@ -14946,16 +14883,16 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B148" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E148" s="12" t="s">
         <v>109</v>
@@ -14995,13 +14932,13 @@
         <v>46090</v>
       </c>
       <c r="B149" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C149" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E149" s="12" t="s">
         <v>109</v>
@@ -15038,16 +14975,16 @@
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B150" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D150" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E150" s="12" t="s">
         <v>109</v>
@@ -15087,13 +15024,13 @@
         <v>46092</v>
       </c>
       <c r="B151" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C151" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E151" s="12" t="s">
         <v>109</v>
@@ -15130,13 +15067,13 @@
         <v>46092</v>
       </c>
       <c r="B152" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C152" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E152" s="12" t="s">
         <v>109</v>
@@ -15176,13 +15113,13 @@
         <v>46094</v>
       </c>
       <c r="B153" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C153" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D153" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E153" s="12" t="s">
         <v>109</v>
@@ -15222,13 +15159,13 @@
         <v>46094</v>
       </c>
       <c r="B154" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C154" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E154" s="12" t="s">
         <v>109</v>
@@ -15268,13 +15205,13 @@
         <v>46094</v>
       </c>
       <c r="B155" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C155" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E155" s="12" t="s">
         <v>109</v>
@@ -15311,13 +15248,13 @@
         <v>46094</v>
       </c>
       <c r="B156" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C156" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E156" s="12" t="s">
         <v>109</v>
@@ -15361,7 +15298,7 @@
         <v>10</v>
       </c>
       <c r="D157" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E157" s="12" t="s">
         <v>109</v>
@@ -15398,13 +15335,13 @@
         <v>46099</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C158" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E158" s="12" t="s">
         <v>109</v>
@@ -15441,13 +15378,13 @@
         <v>46099</v>
       </c>
       <c r="B159" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C159" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D159" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E159" s="12" t="s">
         <v>109</v>
@@ -15484,13 +15421,13 @@
         <v>46099</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D160" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E160" s="12" t="s">
         <v>109</v>
@@ -15501,18 +15438,18 @@
       <c r="G160" s="14"/>
       <c r="H160" s="15"/>
       <c r="I160" s="16"/>
-      <c r="J160" s="15" t="str">
-        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
-        <v/>
+      <c r="J160" s="15">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
+        <v>0</v>
       </c>
       <c r="K160" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L160" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M160" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.3">
@@ -15520,13 +15457,13 @@
         <v>46099</v>
       </c>
       <c r="B161" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C161" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D161" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E161" s="12" t="s">
         <v>109</v>
@@ -15558,7 +15495,7 @@
         <v>38,000.00</v>
       </c>
       <c r="M161" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.3">
@@ -15566,13 +15503,13 @@
         <v>46099</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E162" s="12" t="s">
         <v>109</v>
@@ -15612,13 +15549,13 @@
         <v>46099</v>
       </c>
       <c r="B163" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D163" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E163" s="12" t="s">
         <v>109</v>
@@ -15642,10 +15579,10 @@
         <v/>
       </c>
       <c r="K163" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L163" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M163" s="14" t="s">
         <v>12</v>
@@ -15656,13 +15593,13 @@
         <v>46099</v>
       </c>
       <c r="B164" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D164" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E164" s="12" t="s">
         <v>109</v>
@@ -15699,13 +15636,13 @@
         <v>46100</v>
       </c>
       <c r="B165" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D165" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E165" s="12" t="s">
         <v>11</v>
@@ -15737,7 +15674,7 @@
         <v>56,906.99</v>
       </c>
       <c r="M165" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
@@ -15745,13 +15682,13 @@
         <v>46100</v>
       </c>
       <c r="B166" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C166" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D166" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E166" s="12" t="s">
         <v>11</v>
@@ -15783,7 +15720,7 @@
         <v>56,906.99</v>
       </c>
       <c r="M166" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.3">
@@ -15791,13 +15728,13 @@
         <v>46100</v>
       </c>
       <c r="B167" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C167" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D167" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E167" s="12" t="s">
         <v>11</v>
@@ -15834,13 +15771,13 @@
         <v>46100</v>
       </c>
       <c r="B168" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D168" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E168" s="12" t="s">
         <v>11</v>
@@ -15872,7 +15809,7 @@
         <v>56,906.99</v>
       </c>
       <c r="M168" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
@@ -15880,13 +15817,13 @@
         <v>46100</v>
       </c>
       <c r="B169" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D169" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E169" s="12" t="s">
         <v>11</v>
@@ -15918,7 +15855,7 @@
         <v>56,906.99</v>
       </c>
       <c r="M169" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.3">
@@ -15926,13 +15863,13 @@
         <v>46101</v>
       </c>
       <c r="B170" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D170" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E170" s="12" t="s">
         <v>109</v>
@@ -15969,13 +15906,13 @@
         <v>46102</v>
       </c>
       <c r="B171" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C171" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D171" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E171" s="12" t="s">
         <v>109</v>
@@ -16015,13 +15952,13 @@
         <v>46104</v>
       </c>
       <c r="B172" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D172" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E172" s="12" t="s">
         <v>109</v>
@@ -16034,18 +15971,18 @@
       </c>
       <c r="H172" s="15"/>
       <c r="I172" s="16"/>
-      <c r="J172" s="15" t="str">
-        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
-        <v/>
+      <c r="J172" s="15">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
+        <v>0</v>
       </c>
       <c r="K172" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L172" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M172" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.3">
@@ -16053,13 +15990,13 @@
         <v>46105</v>
       </c>
       <c r="B173" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C173" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D173" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E173" s="12" t="s">
         <v>109</v>
@@ -16091,7 +16028,7 @@
         <v>24,589.37</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.3">
@@ -16099,13 +16036,13 @@
         <v>46107</v>
       </c>
       <c r="B174" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C174" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D174" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E174" s="12" t="s">
         <v>109</v>
@@ -16129,13 +16066,13 @@
         <v/>
       </c>
       <c r="K174" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L174" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M174" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.3">
@@ -16147,7 +16084,7 @@
         <v>10</v>
       </c>
       <c r="D175" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E175" s="12" t="s">
         <v>109</v>
@@ -16163,7 +16100,7 @@
         <v>2990028</v>
       </c>
       <c r="I175" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J175" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -16178,7 +16115,7 @@
         <v>7,890.00</v>
       </c>
       <c r="M175" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.3">
@@ -16190,7 +16127,7 @@
         <v>25</v>
       </c>
       <c r="D176" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E176" s="12" t="s">
         <v>109</v>
@@ -16214,13 +16151,13 @@
         <v/>
       </c>
       <c r="K176" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L176" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M176" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.3">
@@ -16228,13 +16165,13 @@
         <v>46114</v>
       </c>
       <c r="B177" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D177" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E177" s="12" t="s">
         <v>109</v>
@@ -16274,13 +16211,13 @@
         <v>46119</v>
       </c>
       <c r="B178" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C178" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D178" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E178" s="12" t="s">
         <v>109</v>
@@ -16317,13 +16254,13 @@
         <v>46119</v>
       </c>
       <c r="B179" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C179" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E179" s="12" t="s">
         <v>109</v>
@@ -16360,13 +16297,13 @@
         <v>46119</v>
       </c>
       <c r="B180" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D180" s="17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E180" s="12" t="s">
         <v>109</v>
@@ -16398,7 +16335,7 @@
         <v>1,944.77</v>
       </c>
       <c r="M180" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.3">
@@ -16406,13 +16343,13 @@
         <v>46122</v>
       </c>
       <c r="B181" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D181" s="17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E181" s="12" t="s">
         <v>109</v>
@@ -16449,13 +16386,13 @@
         <v>46122</v>
       </c>
       <c r="B182" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D182" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E182" s="12" t="s">
         <v>109</v>
@@ -16484,7 +16421,7 @@
         <v>7,189.50</v>
       </c>
       <c r="M182" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.3">
@@ -16492,13 +16429,13 @@
         <v>46140</v>
       </c>
       <c r="B183" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C183" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D183" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E183" s="12" t="s">
         <v>109</v>
@@ -16530,7 +16467,7 @@
         <v>9,880.00</v>
       </c>
       <c r="M183" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.3">
@@ -16538,13 +16475,13 @@
         <v>46128</v>
       </c>
       <c r="B184" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C184" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D184" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E184" s="12" t="s">
         <v>109</v>
@@ -16560,7 +16497,7 @@
         <v>2993569</v>
       </c>
       <c r="I184" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J184" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -16575,7 +16512,7 @@
         <v>876.80</v>
       </c>
       <c r="M184" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.3">
@@ -16583,13 +16520,13 @@
         <v>46128</v>
       </c>
       <c r="B185" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C185" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D185" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E185" s="12" t="s">
         <v>109</v>
@@ -16626,13 +16563,13 @@
         <v>46128</v>
       </c>
       <c r="B186" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C186" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D186" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E186" s="12" t="s">
         <v>109</v>
@@ -16669,13 +16606,13 @@
         <v>46129</v>
       </c>
       <c r="B187" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C187" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D187" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E187" s="12" t="s">
         <v>109</v>
@@ -16715,7 +16652,7 @@
         <v>46129</v>
       </c>
       <c r="B188" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>10</v>
@@ -16758,13 +16695,13 @@
         <v>46135</v>
       </c>
       <c r="B189" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D189" s="17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E189" s="12" t="s">
         <v>109</v>
@@ -16780,7 +16717,7 @@
         <v>2992797</v>
       </c>
       <c r="I189" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J189" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -16795,7 +16732,7 @@
         <v>1,395.00</v>
       </c>
       <c r="M189" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.3">
@@ -16803,13 +16740,13 @@
         <v>46136</v>
       </c>
       <c r="B190" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C190" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D190" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E190" s="12" t="s">
         <v>109</v>
@@ -16827,10 +16764,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L190" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M190" s="14" t="s">
         <v>12</v>
@@ -16841,13 +16778,13 @@
         <v>46136</v>
       </c>
       <c r="B191" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C191" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D191" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E191" s="12" t="s">
         <v>109</v>
@@ -16879,7 +16816,7 @@
         <v>10,084.67</v>
       </c>
       <c r="M191" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.3">
@@ -16887,13 +16824,13 @@
         <v>46140</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D192" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E192" s="12" t="s">
         <v>109</v>
@@ -16922,7 +16859,7 @@
         <v>18,795.00</v>
       </c>
       <c r="M192" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.3">
@@ -16930,13 +16867,13 @@
         <v>46140</v>
       </c>
       <c r="B193" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C193" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D193" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E193" s="12" t="s">
         <v>109</v>
@@ -16955,10 +16892,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L193" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M193" s="14" t="s">
         <v>12</v>
@@ -16969,13 +16906,13 @@
         <v>46140</v>
       </c>
       <c r="B194" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C194" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D194" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E194" s="12" t="s">
         <v>109</v>
@@ -17007,7 +16944,7 @@
         <v>3,776.01</v>
       </c>
       <c r="M194" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.3">
@@ -17015,13 +16952,13 @@
         <v>46140</v>
       </c>
       <c r="B195" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C195" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D195" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E195" s="12" t="s">
         <v>109</v>
@@ -17050,7 +16987,7 @@
         <v>302.44</v>
       </c>
       <c r="M195" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.3">
@@ -17058,13 +16995,13 @@
         <v>46140</v>
       </c>
       <c r="B196" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C196" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D196" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E196" s="12" t="s">
         <v>109</v>
@@ -17093,7 +17030,7 @@
         <v>1,467.01</v>
       </c>
       <c r="M196" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.3">
@@ -17101,13 +17038,13 @@
         <v>46140</v>
       </c>
       <c r="B197" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D197" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E197" s="12" t="s">
         <v>109</v>
@@ -17125,13 +17062,13 @@
         <v>0</v>
       </c>
       <c r="K197" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L197" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M197" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.3">
@@ -17139,13 +17076,13 @@
         <v>46147</v>
       </c>
       <c r="B198" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D198" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E198" s="12" t="s">
         <v>109</v>
@@ -17161,7 +17098,7 @@
         <v>2994677</v>
       </c>
       <c r="I198" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J198" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -17176,7 +17113,7 @@
         <v>2,402.89</v>
       </c>
       <c r="M198" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.3">
@@ -17184,13 +17121,13 @@
         <v>46148</v>
       </c>
       <c r="B199" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D199" s="17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E199" s="12" t="s">
         <v>109</v>
@@ -17203,13 +17140,13 @@
       <c r="I199" s="16"/>
       <c r="J199" s="15"/>
       <c r="K199" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L199" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M199" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.3">
@@ -17217,13 +17154,13 @@
         <v>46153</v>
       </c>
       <c r="B200" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D200" s="17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E200" s="12" t="s">
         <v>109</v>
@@ -17238,13 +17175,13 @@
       <c r="I200" s="16"/>
       <c r="J200" s="15"/>
       <c r="K200" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="L200" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="L200" s="15" t="s">
-        <v>260</v>
-      </c>
       <c r="M200" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="201" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -17252,13 +17189,13 @@
         <v>46154</v>
       </c>
       <c r="B201" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D201" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E201" s="12" t="s">
         <v>109</v>
@@ -17273,13 +17210,13 @@
       <c r="I201" s="16"/>
       <c r="J201" s="15"/>
       <c r="K201" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L201" s="29">
         <v>1990</v>
       </c>
       <c r="M201" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.3">
@@ -17287,13 +17224,13 @@
         <v>46154</v>
       </c>
       <c r="B202" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E202" s="12" t="s">
         <v>109</v>
@@ -17309,7 +17246,7 @@
         <v>2997755</v>
       </c>
       <c r="I202" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J202" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
@@ -17324,7 +17261,7 @@
         <v>4,930.00</v>
       </c>
       <c r="M202" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="203" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -17332,13 +17269,13 @@
         <v>46155</v>
       </c>
       <c r="B203" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D203" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E203" s="12" t="s">
         <v>109</v>
@@ -17353,13 +17290,13 @@
       <c r="I203" s="16"/>
       <c r="J203" s="15"/>
       <c r="K203" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L203" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M203" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.3">
@@ -17367,13 +17304,13 @@
         <v>46155</v>
       </c>
       <c r="B204" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C204" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D204" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E204" s="12" t="s">
         <v>109</v>
@@ -17388,13 +17325,13 @@
       <c r="I204" s="16"/>
       <c r="J204" s="15"/>
       <c r="K204" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="L204" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="L204" s="15" t="s">
-        <v>256</v>
-      </c>
       <c r="M204" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.3">
@@ -17402,13 +17339,13 @@
         <v>46155</v>
       </c>
       <c r="B205" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D205" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E205" s="12" t="s">
         <v>109</v>
@@ -17423,13 +17360,13 @@
       <c r="I205" s="16"/>
       <c r="J205" s="15"/>
       <c r="K205" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L205" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M205" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.3">
@@ -17437,13 +17374,13 @@
         <v>46160</v>
       </c>
       <c r="B206" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D206" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E206" s="12" t="s">
         <v>109</v>
@@ -17458,13 +17395,13 @@
       <c r="I206" s="16"/>
       <c r="J206" s="15"/>
       <c r="K206" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L206" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M206" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="207" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
@@ -17472,13 +17409,13 @@
         <v>46160</v>
       </c>
       <c r="B207" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D207" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E207" s="12" t="s">
         <v>109</v>
@@ -17493,13 +17430,13 @@
       <c r="I207" s="16"/>
       <c r="J207" s="15"/>
       <c r="K207" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="L207" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="L207" s="15" t="s">
-        <v>252</v>
-      </c>
       <c r="M207" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.3">
@@ -17507,13 +17444,13 @@
         <v>46161</v>
       </c>
       <c r="B208" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D208" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E208" s="12" t="s">
         <v>109</v>
@@ -17528,13 +17465,13 @@
       <c r="I208" s="16"/>
       <c r="J208" s="15"/>
       <c r="K208" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L208" s="29">
         <v>1622.82</v>
       </c>
       <c r="M208" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.3">
@@ -17542,13 +17479,13 @@
         <v>46161</v>
       </c>
       <c r="B209" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D209" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E209" s="12" t="s">
         <v>109</v>
@@ -17561,13 +17498,13 @@
       <c r="I209" s="16"/>
       <c r="J209" s="15"/>
       <c r="K209" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L209" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M209" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.3">
@@ -17575,13 +17512,13 @@
         <v>46162</v>
       </c>
       <c r="B210" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D210" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E210" s="12" t="s">
         <v>109</v>
@@ -17596,13 +17533,13 @@
       <c r="I210" s="16"/>
       <c r="J210" s="15"/>
       <c r="K210" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L210" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M210" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.3">
@@ -17610,13 +17547,13 @@
         <v>46164</v>
       </c>
       <c r="B211" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C211" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D211" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E211" s="12" t="s">
         <v>109</v>
@@ -17629,13 +17566,13 @@
       <c r="I211" s="16"/>
       <c r="J211" s="15"/>
       <c r="K211" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L211" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M211" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.3">
@@ -17643,13 +17580,13 @@
         <v>46164</v>
       </c>
       <c r="B212" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C212" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D212" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E212" s="20" t="s">
         <v>11</v>
@@ -17664,13 +17601,13 @@
       <c r="I212" s="16"/>
       <c r="J212" s="15"/>
       <c r="K212" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="L212" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="L212" s="15" t="s">
-        <v>245</v>
-      </c>
       <c r="M212" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.3">
@@ -17678,13 +17615,13 @@
         <v>46168</v>
       </c>
       <c r="B213" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C213" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D213" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E213" s="20" t="s">
         <v>109</v>
@@ -17699,13 +17636,13 @@
       <c r="I213" s="16"/>
       <c r="J213" s="15"/>
       <c r="K213" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L213" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M213" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.3">
@@ -17713,13 +17650,13 @@
         <v>46168</v>
       </c>
       <c r="B214" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C214" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D214" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E214" s="20" t="s">
         <v>11</v>
@@ -17734,13 +17671,13 @@
       <c r="I214" s="16"/>
       <c r="J214" s="15"/>
       <c r="K214" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L214" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M214" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.3">
@@ -17748,13 +17685,13 @@
         <v>46168</v>
       </c>
       <c r="B215" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C215" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D215" s="17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E215" s="20" t="s">
         <v>109</v>
@@ -17769,197 +17706,197 @@
       <c r="I215" s="16"/>
       <c r="J215" s="15"/>
       <c r="K215" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L215" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M215" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A216" s="38">
+      <c r="A216" s="26">
         <v>46174</v>
       </c>
-      <c r="B216" s="39" t="s">
-        <v>228</v>
+      <c r="B216" s="27" t="s">
+        <v>227</v>
       </c>
       <c r="C216" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D216" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="E216" s="41" t="s">
+      <c r="D216" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="E216" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F216" s="42">
+      <c r="F216" s="19">
         <v>1079039866</v>
       </c>
-      <c r="G216" s="34">
+      <c r="G216" s="14">
         <v>4501746806</v>
       </c>
-      <c r="H216" s="35" t="str">
+      <c r="H216" s="15" t="str">
         <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
         <v>-</v>
       </c>
-      <c r="I216" s="36" t="str">
+      <c r="I216" s="16" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
         <v/>
       </c>
-      <c r="J216" s="37" t="str">
+      <c r="J216" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
         <v/>
       </c>
-      <c r="K216" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="L216" s="35" t="s">
-        <v>295</v>
+      <c r="K216" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="L216" s="15" t="s">
+        <v>294</v>
       </c>
       <c r="M216" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A217" s="31">
+      <c r="A217" s="24">
         <v>46174</v>
       </c>
-      <c r="B217" s="32" t="s">
-        <v>228</v>
+      <c r="B217" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="C217" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D217" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="E217" s="33" t="s">
+      <c r="D217" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="E217" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F217" s="19">
         <v>1079039867</v>
       </c>
-      <c r="G217" s="34"/>
-      <c r="H217" s="35" t="str">
+      <c r="G217" s="14"/>
+      <c r="H217" s="15" t="str">
         <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
         <v>-</v>
       </c>
-      <c r="I217" s="36" t="str">
+      <c r="I217" s="16" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
         <v/>
       </c>
-      <c r="J217" s="37" t="str">
+      <c r="J217" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
         <v/>
       </c>
-      <c r="K217" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="L217" s="35" t="s">
-        <v>294</v>
+      <c r="K217" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="L217" s="15" t="s">
+        <v>293</v>
       </c>
       <c r="M217" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A218" s="31">
+      <c r="A218" s="24">
         <v>46175</v>
       </c>
-      <c r="B218" s="32" t="s">
-        <v>228</v>
+      <c r="B218" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="C218" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D218" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="E218" s="33"/>
+      <c r="D218" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="E218" s="12"/>
       <c r="F218" s="19">
         <v>1079040130</v>
       </c>
-      <c r="G218" s="34"/>
-      <c r="H218" s="35" t="str">
+      <c r="G218" s="14"/>
+      <c r="H218" s="15" t="str">
         <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
         <v>-</v>
       </c>
-      <c r="I218" s="36" t="str">
+      <c r="I218" s="16" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
         <v/>
       </c>
-      <c r="J218" s="37" t="str">
+      <c r="J218" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
         <v/>
       </c>
-      <c r="K218" s="35" t="s">
-        <v>259</v>
-      </c>
-      <c r="L218" s="35" t="s">
-        <v>293</v>
+      <c r="K218" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="L218" s="15" t="s">
+        <v>292</v>
       </c>
       <c r="M218" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A219" s="31">
+      <c r="A219" s="24">
         <v>46182</v>
       </c>
-      <c r="B219" s="32" t="s">
-        <v>228</v>
+      <c r="B219" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="C219" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D219" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="E219" s="33" t="s">
+      <c r="D219" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="E219" s="12" t="s">
         <v>109</v>
       </c>
       <c r="F219" s="19">
         <v>1079140236</v>
       </c>
-      <c r="G219" s="34"/>
-      <c r="H219" s="35" t="str">
+      <c r="G219" s="14"/>
+      <c r="H219" s="15" t="str">
         <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
         <v>-</v>
       </c>
-      <c r="I219" s="36" t="str">
+      <c r="I219" s="16" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
         <v/>
       </c>
-      <c r="J219" s="37" t="str">
+      <c r="J219" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
         <v/>
       </c>
-      <c r="K219" s="35" t="s">
-        <v>290</v>
-      </c>
-      <c r="L219" s="35" t="s">
-        <v>292</v>
+      <c r="K219" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="L219" s="15" t="s">
+        <v>291</v>
       </c>
       <c r="M219" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A220" s="38">
+      <c r="A220" s="26">
         <v>46182</v>
       </c>
-      <c r="B220" s="39" t="s">
-        <v>228</v>
+      <c r="B220" s="27" t="s">
+        <v>227</v>
       </c>
       <c r="C220" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D220" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="E220" s="41" t="s">
+      <c r="D220" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="E220" s="20" t="s">
         <v>109</v>
       </c>
       <c r="F220" s="19">
@@ -17968,221 +17905,221 @@
       <c r="G220" s="14">
         <v>4501749108</v>
       </c>
-      <c r="H220" s="35" t="str">
+      <c r="H220" s="15" t="str">
         <f>IF(Table1[[#This Row],[PEDIDO]]&lt;&gt;"",_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!F:F,"-"),"-")</f>
         <v>-</v>
       </c>
-      <c r="I220" s="36" t="str">
+      <c r="I220" s="16" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!A:A,"")</f>
         <v/>
       </c>
-      <c r="J220" s="37" t="str">
+      <c r="J220" s="15" t="str">
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[VIM]],'[1]BASE DE VIM''s-NF''s'!F:F,'[1]BASE DE VIM''s-NF''s'!L:L,"")</f>
         <v/>
       </c>
-      <c r="K220" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="L220" s="35" t="s">
-        <v>291</v>
+      <c r="K220" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="L220" s="15" t="s">
+        <v>290</v>
       </c>
       <c r="M220" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
+  <conditionalFormatting sqref="A217:D220">
+    <cfRule type="expression" dxfId="48" priority="2">
+      <formula>$F217&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A4:F216 A217:E220">
-    <cfRule type="expression" dxfId="50" priority="53">
+    <cfRule type="expression" dxfId="47" priority="53">
       <formula>$F4&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A206:F206">
-    <cfRule type="expression" dxfId="49" priority="55">
+    <cfRule type="expression" dxfId="46" priority="55">
       <formula>#REF!&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A207:F207">
-    <cfRule type="expression" dxfId="48" priority="54">
+    <cfRule type="expression" dxfId="45" priority="54">
       <formula>$G206&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:G205 E206:E211 A208:D208 F208:G208 G206">
-    <cfRule type="expression" dxfId="47" priority="52">
+    <cfRule type="expression" dxfId="44" priority="52">
       <formula>$G4&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:L202 A203:K204 A205:J205 H206:J206 F206:F207 A206:D208 E206:E211 H207:K207 F208:K208">
-    <cfRule type="expression" dxfId="46" priority="51">
+    <cfRule type="expression" dxfId="43" priority="51">
       <formula>$K4&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A189:L189">
-    <cfRule type="expression" dxfId="45" priority="71">
+    <cfRule type="expression" dxfId="42" priority="71">
       <formula>#REF!="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="69">
+    <cfRule type="expression" dxfId="41" priority="69">
       <formula>#REF!="quadro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="70">
+    <cfRule type="expression" dxfId="40" priority="70">
       <formula>#REF!="finalizado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A190:L190">
-    <cfRule type="expression" dxfId="42" priority="67">
+    <cfRule type="expression" dxfId="39" priority="66">
+      <formula>$M189="quadro"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="67">
       <formula>$M189="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="68">
+    <cfRule type="expression" dxfId="37" priority="68">
       <formula>$M189="cancelado"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="66">
-      <formula>$M189="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:M188 M189:M194 A191:M201 A202:L202 A203:K204 A205:J205 H206:J206 F206:F207 A206:D208 E206:E211 H207:K207 F208:K208">
-    <cfRule type="expression" dxfId="39" priority="48">
+    <cfRule type="expression" dxfId="36" priority="48">
       <formula>$M4="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:M188 M189:M194 A191:M201 M201:M209 A202:L202 A203:K204 A205:J205 H206:J206 F206:F207 A206:D208 E206:E211 H207:K207 F208:K208">
-    <cfRule type="expression" dxfId="38" priority="50">
+    <cfRule type="expression" dxfId="35" priority="50">
       <formula>$M4="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="49">
+    <cfRule type="expression" dxfId="34" priority="49">
       <formula>$M4="finalizado"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F217:F220">
+    <cfRule type="expression" dxfId="33" priority="1">
+      <formula>$F217&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G206">
-    <cfRule type="expression" dxfId="36" priority="56">
+    <cfRule type="expression" dxfId="32" priority="56">
       <formula>$K207&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="57">
+    <cfRule type="expression" dxfId="31" priority="57">
       <formula>$M207="quadro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="58">
+    <cfRule type="expression" dxfId="30" priority="58">
       <formula>$M207="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="59">
+    <cfRule type="expression" dxfId="29" priority="59">
       <formula>$M207="cancelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L2">
-    <cfRule type="expression" dxfId="32" priority="47">
+    <cfRule type="expression" dxfId="28" priority="47">
       <formula>$K2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:M2">
-    <cfRule type="expression" dxfId="31" priority="46">
+    <cfRule type="expression" dxfId="27" priority="46">
       <formula>$M2="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="45">
+    <cfRule type="expression" dxfId="26" priority="45">
       <formula>$M2="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="44">
+    <cfRule type="expression" dxfId="25" priority="44">
       <formula>$M2="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I189:I190">
-    <cfRule type="expression" dxfId="28" priority="3">
+    <cfRule type="expression" dxfId="24" priority="3">
       <formula>$M189="quadro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="4">
+    <cfRule type="expression" dxfId="23" priority="4">
       <formula>$M189="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="5">
+    <cfRule type="expression" dxfId="22" priority="5">
       <formula>$M189="cancelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I209">
-    <cfRule type="expression" dxfId="25" priority="21">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>$M209="quadro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="22">
+    <cfRule type="expression" dxfId="20" priority="22">
       <formula>$M209="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="23">
+    <cfRule type="expression" dxfId="19" priority="23">
       <formula>$M209="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="24">
+    <cfRule type="expression" dxfId="18" priority="24">
       <formula>$K209&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I211">
-    <cfRule type="expression" dxfId="21" priority="14">
-      <formula>$M211="finalizado"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="15">
+    <cfRule type="expression" dxfId="17" priority="15">
       <formula>$M211="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="16">
+    <cfRule type="expression" dxfId="16" priority="16">
       <formula>$K211&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="13">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>$M211="quadro"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="14">
+      <formula>$M211="finalizado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I213">
-    <cfRule type="expression" dxfId="17" priority="28">
+    <cfRule type="expression" dxfId="13" priority="26">
+      <formula>$M213="finalizado"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="28">
       <formula>$K213&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="27">
+    <cfRule type="expression" dxfId="11" priority="27">
       <formula>$M213="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="26">
-      <formula>$M213="finalizado"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="25">
+    <cfRule type="expression" dxfId="10" priority="25">
       <formula>$M213="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I215">
-    <cfRule type="expression" dxfId="13" priority="8">
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>$K215&lt;&gt;""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$M215="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="9">
-      <formula>$K215&lt;&gt;""</formula>
+    <cfRule type="expression" dxfId="7" priority="6">
+      <formula>$M215="quadro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$M215="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6">
-      <formula>$M215="quadro"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M201:M210 M216">
-    <cfRule type="expression" dxfId="9" priority="29">
+  <conditionalFormatting sqref="M201:M210 M212:M216">
+    <cfRule type="expression" dxfId="5" priority="29">
       <formula>$M201="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M210 M216">
-    <cfRule type="expression" dxfId="8" priority="31">
+  <conditionalFormatting sqref="M210 M212:M216">
+    <cfRule type="expression" dxfId="4" priority="31">
       <formula>$M210="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="30">
+    <cfRule type="expression" dxfId="3" priority="30">
       <formula>$M210="finalizado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M212:M215 M218:M220">
-    <cfRule type="expression" dxfId="6" priority="34">
-      <formula>$M212="cancelado"</formula>
+  <conditionalFormatting sqref="M218:M220">
+    <cfRule type="expression" dxfId="2" priority="33">
+      <formula>$M218="finalizado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="32">
-      <formula>$M212="quadro"</formula>
+    <cfRule type="expression" dxfId="1" priority="34">
+      <formula>$M218="cancelado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="33">
-      <formula>$M212="finalizado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A217:D220">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$F217&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F217:F220">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$F217&lt;&gt;""</formula>
+    <cfRule type="expression" dxfId="0" priority="32">
+      <formula>$M218="quadro"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004ppsv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A42E253-F60F-45E8-BD90-6BE5949E9657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EFA1DF-50E4-49FD-8B72-B82AF2D99AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79564DF6-F3EE-4187-9B62-2720CBE5D5A5}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="297">
   <si>
     <t>cancelado</t>
   </si>
@@ -937,6 +937,9 @@
   </si>
   <si>
     <t>1,250,000.00</t>
+  </si>
+  <si>
+    <t>Bloquado</t>
   </si>
 </sst>
 </file>
@@ -9211,7 +9214,9 @@
         <f>_xlfn.XLOOKUP(Table1[[#This Row],[PEDIDO]],'[1]BASE DE VIM''s-NF''s'!I:I,'[1]BASE DE VIM''s-NF''s'!R:R,"")</f>
         <v>179,352.02</v>
       </c>
-      <c r="M21" s="14"/>
+      <c r="M21" s="14" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="24">
